--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035850</v>
+        <v>120035849</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808103</v>
+        <v>808084</v>
       </c>
       <c r="R7" t="n">
-        <v>7172756</v>
+        <v>7172760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035854</v>
+        <v>120035852</v>
       </c>
       <c r="B8" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,21 +1364,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808106</v>
+        <v>808112</v>
       </c>
       <c r="R8" t="n">
-        <v>7172758</v>
+        <v>7172738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035849</v>
+        <v>120035850</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808084</v>
+        <v>808103</v>
       </c>
       <c r="R9" t="n">
-        <v>7172760</v>
+        <v>7172756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035852</v>
+        <v>120035854</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808112</v>
+        <v>808106</v>
       </c>
       <c r="R11" t="n">
-        <v>7172738</v>
+        <v>7172758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120035851</v>
+        <v>120035849</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808101</v>
+        <v>808084</v>
       </c>
       <c r="R6" t="n">
-        <v>7172753</v>
+        <v>7172760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035849</v>
+        <v>120035851</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808084</v>
+        <v>808101</v>
       </c>
       <c r="R7" t="n">
-        <v>7172760</v>
+        <v>7172753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035852</v>
+        <v>120035853</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,21 +1364,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808112</v>
+        <v>808105</v>
       </c>
       <c r="R8" t="n">
-        <v>7172738</v>
+        <v>7172756</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035850</v>
+        <v>120035854</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808103</v>
+        <v>808106</v>
       </c>
       <c r="R9" t="n">
-        <v>7172756</v>
+        <v>7172758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035853</v>
+        <v>120035852</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808105</v>
+        <v>808112</v>
       </c>
       <c r="R10" t="n">
-        <v>7172756</v>
+        <v>7172738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035854</v>
+        <v>120035850</v>
       </c>
       <c r="B11" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,25 +1666,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808106</v>
+        <v>808103</v>
       </c>
       <c r="R11" t="n">
-        <v>7172758</v>
+        <v>7172756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035851</v>
+        <v>120035853</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808101</v>
+        <v>808105</v>
       </c>
       <c r="R7" t="n">
-        <v>7172753</v>
+        <v>7172756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035853</v>
+        <v>120035851</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,21 +1364,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808105</v>
+        <v>808101</v>
       </c>
       <c r="R8" t="n">
-        <v>7172756</v>
+        <v>7172753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120035849</v>
+        <v>120035851</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808084</v>
+        <v>808101</v>
       </c>
       <c r="R6" t="n">
-        <v>7172760</v>
+        <v>7172753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035853</v>
+        <v>120035852</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808105</v>
+        <v>808112</v>
       </c>
       <c r="R7" t="n">
-        <v>7172756</v>
+        <v>7172738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035851</v>
+        <v>120035849</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808101</v>
+        <v>808084</v>
       </c>
       <c r="R8" t="n">
-        <v>7172753</v>
+        <v>7172760</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035854</v>
+        <v>120035853</v>
       </c>
       <c r="B9" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808106</v>
+        <v>808105</v>
       </c>
       <c r="R9" t="n">
-        <v>7172758</v>
+        <v>7172756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035852</v>
+        <v>120035854</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808112</v>
+        <v>808106</v>
       </c>
       <c r="R10" t="n">
-        <v>7172738</v>
+        <v>7172758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120035851</v>
+        <v>120035849</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808101</v>
+        <v>808084</v>
       </c>
       <c r="R6" t="n">
-        <v>7172753</v>
+        <v>7172760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035852</v>
+        <v>120035854</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808112</v>
+        <v>808106</v>
       </c>
       <c r="R7" t="n">
-        <v>7172738</v>
+        <v>7172758</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035849</v>
+        <v>120035852</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808084</v>
+        <v>808112</v>
       </c>
       <c r="R8" t="n">
-        <v>7172760</v>
+        <v>7172738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035853</v>
+        <v>120035850</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808105</v>
+        <v>808103</v>
       </c>
       <c r="R9" t="n">
         <v>7172756</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035854</v>
+        <v>120035853</v>
       </c>
       <c r="B10" t="n">
-        <v>91826</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808106</v>
+        <v>808105</v>
       </c>
       <c r="R10" t="n">
-        <v>7172758</v>
+        <v>7172756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035850</v>
+        <v>120035851</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,25 +1666,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808103</v>
+        <v>808101</v>
       </c>
       <c r="R11" t="n">
-        <v>7172756</v>
+        <v>7172753</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120035849</v>
+        <v>120035851</v>
       </c>
       <c r="B6" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808084</v>
+        <v>808101</v>
       </c>
       <c r="R6" t="n">
-        <v>7172760</v>
+        <v>7172753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035854</v>
+        <v>120035850</v>
       </c>
       <c r="B7" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808106</v>
+        <v>808103</v>
       </c>
       <c r="R7" t="n">
-        <v>7172758</v>
+        <v>7172756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035852</v>
+        <v>120035849</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808112</v>
+        <v>808084</v>
       </c>
       <c r="R8" t="n">
-        <v>7172738</v>
+        <v>7172760</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035850</v>
+        <v>120035854</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>91844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808103</v>
+        <v>808106</v>
       </c>
       <c r="R9" t="n">
-        <v>7172756</v>
+        <v>7172758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035853</v>
+        <v>120035852</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808105</v>
+        <v>808112</v>
       </c>
       <c r="R10" t="n">
-        <v>7172756</v>
+        <v>7172738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035851</v>
+        <v>120035853</v>
       </c>
       <c r="B11" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808101</v>
+        <v>808105</v>
       </c>
       <c r="R11" t="n">
-        <v>7172753</v>
+        <v>7172756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120035851</v>
+        <v>120035850</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808101</v>
+        <v>808103</v>
       </c>
       <c r="R6" t="n">
-        <v>7172753</v>
+        <v>7172756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035850</v>
+        <v>120035852</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808103</v>
+        <v>808112</v>
       </c>
       <c r="R7" t="n">
-        <v>7172756</v>
+        <v>7172738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035854</v>
+        <v>120035851</v>
       </c>
       <c r="B9" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808106</v>
+        <v>808101</v>
       </c>
       <c r="R9" t="n">
-        <v>7172758</v>
+        <v>7172753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035852</v>
+        <v>120035853</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808112</v>
+        <v>808105</v>
       </c>
       <c r="R10" t="n">
-        <v>7172738</v>
+        <v>7172756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035853</v>
+        <v>120035854</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808105</v>
+        <v>808106</v>
       </c>
       <c r="R11" t="n">
-        <v>7172756</v>
+        <v>7172758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035852</v>
+        <v>120035853</v>
       </c>
       <c r="B7" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808112</v>
+        <v>808105</v>
       </c>
       <c r="R7" t="n">
-        <v>7172738</v>
+        <v>7172756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035849</v>
+        <v>120035851</v>
       </c>
       <c r="B8" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808084</v>
+        <v>808101</v>
       </c>
       <c r="R8" t="n">
-        <v>7172760</v>
+        <v>7172753</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035851</v>
+        <v>120035849</v>
       </c>
       <c r="B9" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808101</v>
+        <v>808084</v>
       </c>
       <c r="R9" t="n">
-        <v>7172753</v>
+        <v>7172760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035853</v>
+        <v>120035854</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808105</v>
+        <v>808106</v>
       </c>
       <c r="R10" t="n">
-        <v>7172756</v>
+        <v>7172758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035854</v>
+        <v>120035852</v>
       </c>
       <c r="B11" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808106</v>
+        <v>808112</v>
       </c>
       <c r="R11" t="n">
-        <v>7172758</v>
+        <v>7172738</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120035850</v>
+        <v>120035854</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>91844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808103</v>
+        <v>808106</v>
       </c>
       <c r="R6" t="n">
-        <v>7172756</v>
+        <v>7172758</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035853</v>
+        <v>120035849</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808105</v>
+        <v>808084</v>
       </c>
       <c r="R7" t="n">
-        <v>7172756</v>
+        <v>7172760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035851</v>
+        <v>120035850</v>
       </c>
       <c r="B8" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808101</v>
+        <v>808103</v>
       </c>
       <c r="R8" t="n">
-        <v>7172753</v>
+        <v>7172756</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035849</v>
+        <v>120035851</v>
       </c>
       <c r="B9" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808084</v>
+        <v>808101</v>
       </c>
       <c r="R9" t="n">
-        <v>7172760</v>
+        <v>7172753</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035854</v>
+        <v>120035852</v>
       </c>
       <c r="B10" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1568,21 +1568,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808106</v>
+        <v>808112</v>
       </c>
       <c r="R10" t="n">
-        <v>7172758</v>
+        <v>7172738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035852</v>
+        <v>120035853</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808112</v>
+        <v>808105</v>
       </c>
       <c r="R11" t="n">
-        <v>7172738</v>
+        <v>7172756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035849</v>
+        <v>120035853</v>
       </c>
       <c r="B7" t="n">
-        <v>91870</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808084</v>
+        <v>808105</v>
       </c>
       <c r="R7" t="n">
-        <v>7172760</v>
+        <v>7172756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035851</v>
+        <v>120035849</v>
       </c>
       <c r="B9" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808101</v>
+        <v>808084</v>
       </c>
       <c r="R9" t="n">
-        <v>7172753</v>
+        <v>7172760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035853</v>
+        <v>120035851</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808105</v>
+        <v>808101</v>
       </c>
       <c r="R11" t="n">
-        <v>7172756</v>
+        <v>7172753</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 16152-2021 artfynd.xlsx
+++ b/artfynd/A 16152-2021 artfynd.xlsx
@@ -1144,10 +1144,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120035854</v>
+        <v>120035851</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,21 +1160,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>808106</v>
+        <v>808101</v>
       </c>
       <c r="R6" t="n">
-        <v>7172758</v>
+        <v>7172753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120035853</v>
+        <v>120035850</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1258,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>808105</v>
+        <v>808103</v>
       </c>
       <c r="R7" t="n">
         <v>7172756</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120035850</v>
+        <v>120035853</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>808103</v>
+        <v>808105</v>
       </c>
       <c r="R8" t="n">
         <v>7172756</v>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120035849</v>
+        <v>120035852</v>
       </c>
       <c r="B9" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,25 +1462,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>808084</v>
+        <v>808112</v>
       </c>
       <c r="R9" t="n">
-        <v>7172760</v>
+        <v>7172738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120035852</v>
+        <v>120035849</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,25 +1564,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>808112</v>
+        <v>808084</v>
       </c>
       <c r="R10" t="n">
-        <v>7172738</v>
+        <v>7172760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120035851</v>
+        <v>120035854</v>
       </c>
       <c r="B11" t="n">
-        <v>91902</v>
+        <v>91844</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>808101</v>
+        <v>808106</v>
       </c>
       <c r="R11" t="n">
-        <v>7172753</v>
+        <v>7172758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
